--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB22"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -2647,12 +2647,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
+          <t>Ampliación Mega</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
+          <t>Ampliación de un complejo industrial para incrementar la capacidad de producción de Líquidos del Gas Natural (LGN) en 1500 toneladas diarias.  El proyecto contempla nuevas instalaciones en la Planta de Separación de Loma La Lata, la ampliación de la capacidad de transporte del poliducto que atraviesa Neuquén, Río Negro, La Pampa y Buenos Aires, y la expansión de la Planta de Fraccionamiento ubicada en Bahía Blanca.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2661,21 +2661,21 @@
         </is>
       </c>
       <c r="D21">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE) (Argentina)</t>
+          <t>YPF S.A. (Argentina); Petrobras (Brasil); Dow (Argentina)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE)</t>
+          <t>Compañía Mega SA Sucursal Dedicada</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t> 30-71703621-9</t>
+          <t>30-71932893-4</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2690,36 +2690,36 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Transporte y Almacenamiento</t>
+          <t>Construcción de plantas de tratamiento, plantas de separación de líquidos de gas natural, oleoductos, gasoductos y poliductos e instalaciones de almacenamiento</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Río Negro; Neuquén</t>
+          <t>Neuquén; La Pampa; Río Negro; Buenos Aires</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Múltiples</t>
         </is>
       </c>
       <c r="M21">
-        <v>1300</v>
+        <v>365.398669</v>
       </c>
       <c r="N21">
-        <v>1300</v>
+        <v>365.398669</v>
       </c>
       <c r="O21">
-        <v>955</v>
+        <v>359.164361</v>
       </c>
       <c r="P21">
-        <v>454</v>
+        <v>121.613889</v>
       </c>
       <c r="Q21">
-        <v>501</v>
+        <v>152.709106</v>
       </c>
       <c r="R21">
-        <v>955</v>
+        <v>274.322995</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2727,144 +2727,257 @@
         </is>
       </c>
       <c r="T21">
-        <v>2489</v>
+        <v>792</v>
       </c>
       <c r="U21" s="2">
-        <v>46538</v>
+        <v>46661</v>
       </c>
       <c r="V21" s="2">
-        <v>45950</v>
+        <v>46099</v>
       </c>
       <c r="W21" s="2">
-        <v>46174</v>
+        <v>46231</v>
       </c>
       <c r="X21" s="2">
-        <v>46198</v>
+        <v>46260</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Res. 873/2026</t>
+          <t>Res. 1381/2026</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346397/20260826</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Res. 873/2026; Globaris; MECON</t>
+          <t>Res. 1381/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>36</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pan American Energy (PAE) (Argentina)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pan American Energy (PAE)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t> 30-71703621-9</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Midstream</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Transporte y Almacenamiento</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Río Negro; Neuquén</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="M22">
+        <v>1300</v>
+      </c>
+      <c r="N22">
+        <v>1300</v>
+      </c>
+      <c r="O22">
+        <v>955</v>
+      </c>
+      <c r="P22">
+        <v>454</v>
+      </c>
+      <c r="Q22">
+        <v>501</v>
+      </c>
+      <c r="R22">
+        <v>955</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="T22">
+        <v>2489</v>
+      </c>
+      <c r="U22" s="2">
+        <v>46538</v>
+      </c>
+      <c r="V22" s="2">
+        <v>45950</v>
+      </c>
+      <c r="W22" s="2">
+        <v>46174</v>
+      </c>
+      <c r="X22" s="2">
+        <v>46198</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Res. 873/2026</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Res. 873/2026; Globaris; MECON</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Hombre Muerto Oeste (HMW)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Producción de doce mil (12.000) toneladas anuales de carbonato de litio equivalente (LCE)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D22">
+      <c r="D23">
         <v>37</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Galan Lithium Ltd (Australia)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Galan Litio SA</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>30-71899846-4</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Litio</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Potasio y Litio</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Catamarca</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="M22">
+      <c r="M23">
         <v>292</v>
       </c>
-      <c r="N22">
+      <c r="N23">
         <v>217</v>
       </c>
-      <c r="O22">
+      <c r="O23">
         <v>217</v>
       </c>
-      <c r="P22">
+      <c r="P23">
         <v>31.112863</v>
       </c>
-      <c r="Q22">
+      <c r="Q23">
         <v>51.531371</v>
       </c>
-      <c r="R22">
+      <c r="R23">
         <v>82.644234</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="T22">
+      <c r="T23">
         <v>670</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U23" s="2">
         <v>47483</v>
       </c>
-      <c r="V22" s="2">
+      <c r="V23" s="2">
         <v>45594</v>
       </c>
-      <c r="W22" s="2">
+      <c r="W23" s="2">
         <v>45855</v>
       </c>
-      <c r="X22" s="2">
+      <c r="X23" s="2">
         <v>45896</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Res. 1271/2025</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/330470/20250828</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>Res. 1271/2025; Globaris; MECON</t>
         </is>

--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -2760,35 +2760,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
+          <t>Fertilizantes</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
+          <t>Construcción, operación y gerenciamiento de dos (2) plantas de producción de urea, cada una con capacidad de tres mil toneladas (3.000 t) por día, con sus correspondientes unidades de granulación, y una planta de amoníaco con capacidad de tres mil cuatrocientas cincuenta toneladas (3.450 t) por día, utilizando como insumo principal el gas natural de Vaca Muerta, a desarrollarse en el Puerto de Ingeniero White, partido de Bahía Blanca, provincia de Buenos Aires.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE) (Argentina)</t>
+          <t>Pampa Energía (Argentina)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE)</t>
+          <t>Fértil Pampa S.A.U.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t> 30-71703621-9</t>
+          <t>30-71875855-2</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2798,41 +2798,41 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Petroquímica y Fertilizantes</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Transporte y Almacenamiento</t>
+          <t>Petroquímica y Fertilizantes</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Río Negro; Neuquén</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Puerto de Ingeniero White, Bahía Blanca</t>
         </is>
       </c>
       <c r="M22">
-        <v>1300</v>
+        <v>2693</v>
       </c>
       <c r="N22">
-        <v>1300</v>
+        <v>2693</v>
       </c>
       <c r="O22">
-        <v>955</v>
+        <v>2693</v>
       </c>
       <c r="P22">
-        <v>454</v>
+        <v>785</v>
       </c>
       <c r="Q22">
-        <v>501</v>
+        <v>881</v>
       </c>
       <c r="R22">
-        <v>955</v>
+        <v>1666</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2840,144 +2840,257 @@
         </is>
       </c>
       <c r="T22">
-        <v>2489</v>
+        <v>12500</v>
       </c>
       <c r="U22" s="2">
-        <v>46538</v>
+        <v>47453</v>
       </c>
       <c r="V22" s="2">
-        <v>45950</v>
+        <v>46237</v>
       </c>
       <c r="W22" s="2">
-        <v>46174</v>
+        <v>46237</v>
       </c>
       <c r="X22" s="2">
-        <v>46198</v>
+        <v>46272</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Res. 873/2026</t>
+          <t>Res. 1468/2026</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346966/20260907</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Res. 873/2026; Globaris; MECON</t>
+          <t>Res.1468/2026; MECON</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>36</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Pan American Energy (PAE) (Argentina)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pan American Energy (PAE)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t> 30-71703621-9</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Midstream</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Transporte y Almacenamiento</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Río Negro; Neuquén</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="M23">
+        <v>1300</v>
+      </c>
+      <c r="N23">
+        <v>1300</v>
+      </c>
+      <c r="O23">
+        <v>955</v>
+      </c>
+      <c r="P23">
+        <v>454</v>
+      </c>
+      <c r="Q23">
+        <v>501</v>
+      </c>
+      <c r="R23">
+        <v>955</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="T23">
+        <v>2489</v>
+      </c>
+      <c r="U23" s="2">
+        <v>46538</v>
+      </c>
+      <c r="V23" s="2">
+        <v>45950</v>
+      </c>
+      <c r="W23" s="2">
+        <v>46174</v>
+      </c>
+      <c r="X23" s="2">
+        <v>46198</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Res. 873/2026</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Res. 873/2026; Globaris; MECON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Hombre Muerto Oeste (HMW)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Producción de doce mil (12.000) toneladas anuales de carbonato de litio equivalente (LCE)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D23">
+      <c r="D24">
         <v>37</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Galan Lithium Ltd (Australia)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Galan Litio SA</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>30-71899846-4</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Litio</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Potasio y Litio</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Catamarca</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="M23">
+      <c r="M24">
         <v>292</v>
       </c>
-      <c r="N23">
+      <c r="N24">
         <v>217</v>
       </c>
-      <c r="O23">
+      <c r="O24">
         <v>217</v>
       </c>
-      <c r="P23">
+      <c r="P24">
         <v>31.112863</v>
       </c>
-      <c r="Q23">
+      <c r="Q24">
         <v>51.531371</v>
       </c>
-      <c r="R23">
+      <c r="R24">
         <v>82.644234</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="T23">
+      <c r="T24">
         <v>670</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U24" s="2">
         <v>47483</v>
       </c>
-      <c r="V23" s="2">
+      <c r="V24" s="2">
         <v>45594</v>
       </c>
-      <c r="W23" s="2">
+      <c r="W24" s="2">
         <v>45855</v>
       </c>
-      <c r="X23" s="2">
+      <c r="X24" s="2">
         <v>45896</v>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Res. 1271/2025</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/330470/20250828</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>Res. 1271/2025; Globaris; MECON</t>
         </is>

--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -2846,7 +2846,7 @@
         <v>47453</v>
       </c>
       <c r="V22" s="2">
-        <v>46237</v>
+        <v>46133</v>
       </c>
       <c r="W22" s="2">
         <v>46237</v>

--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -2896,7 +2896,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE)</t>
+          <t>San Matías Pipeline S.A.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">

--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -2087,12 +2087,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Proyecto Rincón de Aranda (RDA)</t>
+          <t>UT RIGI LOS TOLDOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Consiste en: (i) la explotación de nuevos pozos hidrocarburíferos en el área RDA; (ii) el desarrollo, operación y/o prestación del servicio de tratamiento, procesamiento, almacenamiento y transporte del petróleo, gas natural y agua extraídos por PAMPA ENERGÍA SOCIEDAD ANÓNIMA - SUCURSAL DEDICADA PROYECTO RDA del área RDA y/o prestados a terceros, y la disposición final del agua incluyendo, la construcción y operación de plantas, oleoductos y gasoductos; y en (iii) la exportación y/o comercialización de los hidrocarburos y sus derivados obtenidos de la explotación de los nuevos pozos a desarrollarse en el área RDA.</t>
+          <t>Desarrollo de hidrocarburos en el área Los Toldos II Este, Vaca Muerta, el cual consiste en la perforación de 380 pozos junto con su infraestructura asociada para el tratamiento de la producción por una capacidad máxima de 70 mil barriles de petróleo diarios. El proyecto prevé un total de 360 millones de barriles de petróleo de exportación durante su operación.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="D16">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pampa Energía (Argentina)</t>
+          <t>Tecpetrol S.A. (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sucursal Dedicada Midstream RDA</t>
+          <t>Tecpetrol S.A. Gas y Petróleo del Neuquén S.A. UT RIGI Los Toldos U.T.E.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30-71901911-7</t>
+          <t>33-71889684-9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Explotación y Producción de Hidrocarburos Líquidos y Gaseosos Costa Adentro</t>
+          <t>Explotación y producción de nuevos desarrollos de hidrocarburos líquidos y gaseosos costa adentro</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2140,26 +2140,23 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Departamento Pehuenches; área Los Toldos II Este; Engolfamiento/Bajo de Añelo</t>
         </is>
       </c>
       <c r="M16">
-        <v>4522</v>
+        <v>6432</v>
       </c>
       <c r="N16">
-        <v>4521</v>
-      </c>
-      <c r="O16">
-        <v>4521</v>
+        <v>6432</v>
       </c>
       <c r="P16">
-        <v>521</v>
+        <v>1182.281332</v>
       </c>
       <c r="Q16">
-        <v>578</v>
+        <v>577.9334679999999</v>
       </c>
       <c r="R16">
-        <v>1099</v>
+        <v>1760.2148</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2167,112 +2164,117 @@
         </is>
       </c>
       <c r="T16">
-        <v>1733</v>
+        <v>7900</v>
       </c>
       <c r="U16" s="2">
-        <v>48030</v>
+        <v>46630</v>
       </c>
       <c r="V16" s="2">
-        <v>46090</v>
+        <v>46101</v>
       </c>
       <c r="W16" s="2">
-        <v>46198</v>
+        <v>46274</v>
       </c>
       <c r="X16" s="2">
-        <v>46224</v>
+        <v>46304</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Res. 1025/2026</t>
+          <t>Res. 1771/2026</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/344628/20260721</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/348768/20261009</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Res. 1025/2026; Globaris; MECON</t>
+          <t>Res. 1771/2026; Tecpetrol</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/normativa/nacional/norma-431089 ; https://www.tecpetrol.com/es/noticias/2026/rigi-los-toldos-ii-este</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sal de Oro II</t>
+          <t>Proyecto Rincón de Aranda (RDA)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Construcción de una planta destinada a la producción de carbonato de litio y su infraestructura complementaria. La planta tendrá una capacidad operativa aproximada de 23.000 toneladas anuales, que se obtendrá a través de un proceso convencional de evaporación solar y tratamiento químico de salmuera.</t>
+          <t>Consiste en: (i) la explotación de nuevos pozos hidrocarburíferos en el área RDA; (ii) el desarrollo, operación y/o prestación del servicio de tratamiento, procesamiento, almacenamiento y transporte del petróleo, gas natural y agua extraídos por PAMPA ENERGÍA SOCIEDAD ANÓNIMA - SUCURSAL DEDICADA PROYECTO RDA del área RDA y/o prestados a terceros, y la disposición final del agua incluyendo, la construcción y operación de plantas, oleoductos y gasoductos; y en (iii) la exportación y/o comercialización de los hidrocarburos y sus derivados obtenidos de la explotación de los nuevos pozos a desarrollarse en el área RDA.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Posco (Corea del Sur)</t>
+          <t>Pampa Energía (Argentina)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Posco Argentina SAU SDE</t>
+          <t>Sucursal Dedicada Midstream RDA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30-71922048-3</t>
+          <t>30-71901911-7</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Potasio y Litio</t>
+          <t>Explotación y Producción de Hidrocarburos Líquidos y Gaseosos Costa Adentro</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Salta; Catamarca</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="M17">
-        <v>547</v>
+        <v>4522</v>
       </c>
       <c r="N17">
-        <v>547</v>
+        <v>4521</v>
       </c>
       <c r="O17">
-        <v>208</v>
+        <v>4521</v>
       </c>
       <c r="P17">
-        <v>90.916876</v>
+        <v>521</v>
       </c>
       <c r="Q17">
-        <v>7.083124</v>
+        <v>578</v>
       </c>
       <c r="R17">
-        <v>98</v>
+        <v>1099</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2280,63 +2282,68 @@
         </is>
       </c>
       <c r="T17">
-        <v>2335</v>
+        <v>1733</v>
       </c>
       <c r="U17" s="2">
-        <v>47330</v>
+        <v>48030</v>
       </c>
       <c r="V17" s="2">
-        <v>45595</v>
+        <v>46090</v>
       </c>
       <c r="W17" s="2">
-        <v>46185</v>
+        <v>46198</v>
       </c>
       <c r="X17" s="2">
-        <v>46234</v>
+        <v>46224</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Res. 1157/2026</t>
+          <t>Res. 1025/2026</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345279/20260731</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/344628/20260721</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Res. 1157/2026; Globaris; MECON</t>
+          <t>Res. 1025/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Proyecto de la Sucursal Dedicada de Liex S.A.</t>
+          <t>Sal de Oro II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Construcción y operación de una planta de proceso y de la infraestructura asociada, diseñadas para alcanzar una capacidad de producción de cuarenta mil (40.000) toneladas anuales de carbonato de litio mediante el método de extracción directa</t>
+          <t>Construcción de una planta destinada a la producción de carbonato de litio y su infraestructura complementaria. La planta tendrá una capacidad operativa aproximada de 23.000 toneladas anuales, que se obtendrá a través de un proceso convencional de evaporación solar y tratamiento químico de salmuera.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="D18">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zijin Mining (China)</t>
+          <t>Posco (Corea del Sur)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LIEX S.A.</t>
+          <t>Posco Argentina SAU SDE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>30-71929244-1</t>
+          <t>30-71922048-3</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2356,7 +2363,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Salta; Catamarca</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2365,22 +2372,22 @@
         </is>
       </c>
       <c r="M18">
-        <v>710</v>
+        <v>547</v>
       </c>
       <c r="N18">
-        <v>710</v>
+        <v>547</v>
       </c>
       <c r="O18">
-        <v>594</v>
+        <v>208</v>
       </c>
       <c r="P18">
-        <v>107.537</v>
+        <v>90.916876</v>
       </c>
       <c r="Q18">
-        <v>308.048</v>
+        <v>7.083124</v>
       </c>
       <c r="R18">
-        <v>415.585</v>
+        <v>98</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2388,68 +2395,63 @@
         </is>
       </c>
       <c r="T18">
-        <v>4406</v>
+        <v>2335</v>
       </c>
       <c r="U18" s="2">
-        <v>46721</v>
+        <v>47330</v>
       </c>
       <c r="V18" s="2">
-        <v>46063</v>
+        <v>45595</v>
       </c>
       <c r="W18" s="2">
-        <v>46206</v>
+        <v>46185</v>
       </c>
       <c r="X18" s="2">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Res. 1153/2026</t>
+          <t>Res. 1157/2026</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345075/20260729</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345279/20260731</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Res. 1153/2026; Globaris; MECON</t>
+          <t>Res. 1157/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Proyecto de la Sucursal Dedicada de Liex S.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Extracción, producción y exportación de cobre, oro y plata de los yacimientos Josemaría y Filo del Sol ubicados en la provincia de San Juan, República Argentina, así como la exploración de las concesiones mineras que forman parte del proyecto y el desarrollo de la infraestructura necesaria para su ejecución. Incluye infraestructura clave para operaciones de minería a cielo abierto: una planta concentradora para el procesamiento de minerales, instalaciones de lixiviación, infraestructura eléctrica, sistemas de suministro de agua, caminos de acceso y alojamientos.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Construcción y operación de una planta de proceso y de la infraestructura asociada, diseñadas para alcanzar una capacidad de producción de cuarenta mil (40.000) toneladas anuales de carbonato de litio mediante el método de extracción directa</t>
         </is>
       </c>
       <c r="D19">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BHP (Australia); Lundin Mining (Canadá)</t>
+          <t>Zijin Mining (China)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vicuña Argentina S.A.</t>
+          <t>LIEX S.A.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>33-61913055-9</t>
+          <t>30-71929244-1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2459,41 +2461,41 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cobre, Oro y Plata</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Minerales de primera y segunda categoría del Código de Minería de la Nación (excluidos potasio y litio)</t>
+          <t>Potasio y Litio</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cuyo</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="M19">
-        <v>9737</v>
+        <v>710</v>
       </c>
       <c r="N19">
-        <v>9737</v>
+        <v>710</v>
       </c>
       <c r="O19">
-        <v>9025</v>
+        <v>594</v>
       </c>
       <c r="P19">
-        <v>1004.6565</v>
+        <v>107.537</v>
       </c>
       <c r="Q19">
-        <v>1004.6565</v>
+        <v>308.048</v>
       </c>
       <c r="R19">
-        <v>2009.313</v>
+        <v>415.585</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2501,68 +2503,68 @@
         </is>
       </c>
       <c r="T19">
-        <v>31700</v>
+        <v>4406</v>
       </c>
       <c r="U19" s="2">
-        <v>47118</v>
+        <v>46721</v>
       </c>
       <c r="V19" s="2">
-        <v>46002</v>
+        <v>46063</v>
       </c>
       <c r="W19" s="2">
-        <v>46176</v>
+        <v>46206</v>
       </c>
       <c r="X19" s="2">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Res. 1154/2026</t>
+          <t>Res. 1153/2026</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345167/20260730</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345075/20260729</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Res. 1154/2026; Globaris; MECON</t>
+          <t>Res. 1153/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Proyecto Los Azules</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Desarrollo (factibilidad, permisos) y la construcción de mina, planta e infraestructura asociada para extraer y procesar cátodos de cobre</t>
+          <t>Extracción, producción y exportación de cobre, oro y plata de los yacimientos Josemaría y Filo del Sol ubicados en la provincia de San Juan, República Argentina, así como la exploración de las concesiones mineras que forman parte del proyecto y el desarrollo de la infraestructura necesaria para su ejecución. Incluye infraestructura clave para operaciones de minería a cielo abierto: una planta concentradora para el procesamiento de minerales, instalaciones de lixiviación, infraestructura eléctrica, sistemas de suministro de agua, caminos de acceso y alojamientos.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D20">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>McEwen Copper Inc. (Canadá)</t>
+          <t>BHP (Australia); Lundin Mining (Canadá)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Andes Corporación Minera SA (ACM)</t>
+          <t>Vicuña Argentina S.A.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>30-70952278-3</t>
+          <t>33-61913055-9</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2572,7 +2574,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Cobre, Oro y Plata</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2591,22 +2593,22 @@
         </is>
       </c>
       <c r="M20">
-        <v>2672</v>
+        <v>9737</v>
       </c>
       <c r="N20">
-        <v>2672</v>
+        <v>9737</v>
       </c>
       <c r="O20">
-        <v>2354</v>
+        <v>9025</v>
       </c>
       <c r="P20">
-        <v>33.51255105</v>
+        <v>1004.6565</v>
       </c>
       <c r="Q20">
-        <v>382.26276161</v>
+        <v>1004.6565</v>
       </c>
       <c r="R20">
-        <v>415.77531266</v>
+        <v>2009.313</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2614,45 +2616,45 @@
         </is>
       </c>
       <c r="T20">
-        <v>7391</v>
+        <v>31700</v>
       </c>
       <c r="U20" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="V20" s="2">
-        <v>45849</v>
+        <v>46002</v>
       </c>
       <c r="W20" s="2">
-        <v>45925</v>
+        <v>46176</v>
       </c>
       <c r="X20" s="2">
-        <v>45943</v>
+        <v>46233</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Res. 1553/2025</t>
+          <t>Res. 1154/2026</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/332807/20251014</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345167/20260730</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Res. 1553/2025; Globaris; MECON</t>
+          <t>Res. 1154/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ampliación Mega</t>
+          <t>Proyecto Los Azules</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ampliación de un complejo industrial para incrementar la capacidad de producción de Líquidos del Gas Natural (LGN) en 1500 toneladas diarias.  El proyecto contempla nuevas instalaciones en la Planta de Separación de Loma La Lata, la ampliación de la capacidad de transporte del poliducto que atraviesa Neuquén, Río Negro, La Pampa y Buenos Aires, y la expansión de la Planta de Fraccionamiento ubicada en Bahía Blanca.</t>
+          <t>Desarrollo (factibilidad, permisos) y la construcción de mina, planta e infraestructura asociada para extraer y procesar cátodos de cobre</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2661,65 +2663,65 @@
         </is>
       </c>
       <c r="D21">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina); Petrobras (Brasil); Dow (Argentina)</t>
+          <t>McEwen Copper Inc. (Canadá)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Compañía Mega SA Sucursal Dedicada</t>
+          <t>Andes Corporación Minera SA (ACM)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>30-71932893-4</t>
+          <t>30-70952278-3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Construcción de plantas de tratamiento, plantas de separación de líquidos de gas natural, oleoductos, gasoductos y poliductos e instalaciones de almacenamiento</t>
+          <t>Minerales de primera y segunda categoría del Código de Minería de la Nación (excluidos potasio y litio)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Neuquén; La Pampa; Río Negro; Buenos Aires</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Múltiples</t>
+          <t>Cuyo</t>
         </is>
       </c>
       <c r="M21">
-        <v>365.398669</v>
+        <v>2672</v>
       </c>
       <c r="N21">
-        <v>365.398669</v>
+        <v>2672</v>
       </c>
       <c r="O21">
-        <v>359.164361</v>
+        <v>2354</v>
       </c>
       <c r="P21">
-        <v>121.613889</v>
+        <v>33.51255105</v>
       </c>
       <c r="Q21">
-        <v>152.709106</v>
+        <v>382.26276161</v>
       </c>
       <c r="R21">
-        <v>274.322995</v>
+        <v>415.77531266</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2727,68 +2729,68 @@
         </is>
       </c>
       <c r="T21">
-        <v>792</v>
+        <v>7391</v>
       </c>
       <c r="U21" s="2">
-        <v>46661</v>
+        <v>46752</v>
       </c>
       <c r="V21" s="2">
-        <v>46099</v>
+        <v>45849</v>
       </c>
       <c r="W21" s="2">
-        <v>46231</v>
+        <v>45925</v>
       </c>
       <c r="X21" s="2">
-        <v>46260</v>
+        <v>45943</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Res. 1381/2026</t>
+          <t>Res. 1553/2025</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346397/20260826</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/332807/20251014</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Res. 1381/2026; Globaris; MECON</t>
+          <t>Res. 1553/2025; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fertilizantes</t>
+          <t>Ampliación Mega</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Construcción, operación y gerenciamiento de dos (2) plantas de producción de urea, cada una con capacidad de tres mil toneladas (3.000 t) por día, con sus correspondientes unidades de granulación, y una planta de amoníaco con capacidad de tres mil cuatrocientas cincuenta toneladas (3.450 t) por día, utilizando como insumo principal el gas natural de Vaca Muerta, a desarrollarse en el Puerto de Ingeniero White, partido de Bahía Blanca, provincia de Buenos Aires.</t>
+          <t>Ampliación de un complejo industrial para incrementar la capacidad de producción de Líquidos del Gas Natural (LGN) en 1500 toneladas diarias.  El proyecto contempla nuevas instalaciones en la Planta de Separación de Loma La Lata, la ampliación de la capacidad de transporte del poliducto que atraviesa Neuquén, Río Negro, La Pampa y Buenos Aires, y la expansión de la Planta de Fraccionamiento ubicada en Bahía Blanca.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D22">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pampa Energía (Argentina)</t>
+          <t>YPF S.A. (Argentina); Petrobras (Brasil); Dow (Argentina)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fértil Pampa S.A.U.</t>
+          <t>Compañía Mega SA Sucursal Dedicada</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>30-71875855-2</t>
+          <t>30-71932893-4</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2798,41 +2800,41 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Petroquímica y Fertilizantes</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Petroquímica y Fertilizantes</t>
+          <t>Construcción de plantas de tratamiento, plantas de separación de líquidos de gas natural, oleoductos, gasoductos y poliductos e instalaciones de almacenamiento</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Neuquén; La Pampa; Río Negro; Buenos Aires</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Puerto de Ingeniero White, Bahía Blanca</t>
+          <t>Múltiples</t>
         </is>
       </c>
       <c r="M22">
-        <v>2693</v>
+        <v>365.398669</v>
       </c>
       <c r="N22">
-        <v>2693</v>
+        <v>365.398669</v>
       </c>
       <c r="O22">
-        <v>2693</v>
+        <v>359.164361</v>
       </c>
       <c r="P22">
-        <v>785</v>
+        <v>121.613889</v>
       </c>
       <c r="Q22">
-        <v>881</v>
+        <v>152.709106</v>
       </c>
       <c r="R22">
-        <v>1666</v>
+        <v>274.322995</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2840,68 +2842,68 @@
         </is>
       </c>
       <c r="T22">
-        <v>12500</v>
+        <v>792</v>
       </c>
       <c r="U22" s="2">
-        <v>47453</v>
+        <v>46661</v>
       </c>
       <c r="V22" s="2">
-        <v>46133</v>
+        <v>46099</v>
       </c>
       <c r="W22" s="2">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="X22" s="2">
-        <v>46272</v>
+        <v>46260</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Res. 1468/2026</t>
+          <t>Res. 1381/2026</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346966/20260907</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346397/20260826</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Res.1468/2026; MECON</t>
+          <t>Res. 1381/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
+          <t>Fertilizantes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
+          <t>Construcción, operación y gerenciamiento de dos (2) plantas de producción de urea, cada una con capacidad de tres mil toneladas (3.000 t) por día, con sus correspondientes unidades de granulación, y una planta de amoníaco con capacidad de tres mil cuatrocientas cincuenta toneladas (3.450 t) por día, utilizando como insumo principal el gas natural de Vaca Muerta, a desarrollarse en el Puerto de Ingeniero White, partido de Bahía Blanca, provincia de Buenos Aires.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D23">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE) (Argentina)</t>
+          <t>Pampa Energía (Argentina)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>San Matías Pipeline S.A.</t>
+          <t>Fértil Pampa S.A.U.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t> 30-71703621-9</t>
+          <t>30-71875855-2</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2911,41 +2913,41 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Petroquímica y Fertilizantes</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Transporte y Almacenamiento</t>
+          <t>Petroquímica y Fertilizantes</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Río Negro; Neuquén</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Puerto de Ingeniero White, Bahía Blanca</t>
         </is>
       </c>
       <c r="M23">
-        <v>1300</v>
+        <v>2693</v>
       </c>
       <c r="N23">
-        <v>1300</v>
+        <v>2693</v>
       </c>
       <c r="O23">
-        <v>955</v>
+        <v>2693</v>
       </c>
       <c r="P23">
-        <v>454</v>
+        <v>785</v>
       </c>
       <c r="Q23">
-        <v>501</v>
+        <v>881</v>
       </c>
       <c r="R23">
-        <v>955</v>
+        <v>1666</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2953,144 +2955,257 @@
         </is>
       </c>
       <c r="T23">
-        <v>2489</v>
+        <v>12500</v>
       </c>
       <c r="U23" s="2">
-        <v>46538</v>
+        <v>47453</v>
       </c>
       <c r="V23" s="2">
-        <v>45950</v>
+        <v>46133</v>
       </c>
       <c r="W23" s="2">
-        <v>46174</v>
+        <v>46237</v>
       </c>
       <c r="X23" s="2">
-        <v>46198</v>
+        <v>46272</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Res. 873/2026</t>
+          <t>Res. 1468/2026</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346966/20260907</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Res. 873/2026; Globaris; MECON</t>
+          <t>Res.1468/2026; MECON</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>36</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pan American Energy (PAE) (Argentina)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>San Matías Pipeline S.A.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t> 30-71703621-9</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Midstream</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Transporte y Almacenamiento</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Río Negro; Neuquén</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="M24">
+        <v>1300</v>
+      </c>
+      <c r="N24">
+        <v>1300</v>
+      </c>
+      <c r="O24">
+        <v>955</v>
+      </c>
+      <c r="P24">
+        <v>454</v>
+      </c>
+      <c r="Q24">
+        <v>501</v>
+      </c>
+      <c r="R24">
+        <v>955</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="T24">
+        <v>2489</v>
+      </c>
+      <c r="U24" s="2">
+        <v>46538</v>
+      </c>
+      <c r="V24" s="2">
+        <v>45950</v>
+      </c>
+      <c r="W24" s="2">
+        <v>46174</v>
+      </c>
+      <c r="X24" s="2">
+        <v>46198</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Res. 873/2026</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Res. 873/2026; Globaris; MECON</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Hombre Muerto Oeste (HMW)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Producción de doce mil (12.000) toneladas anuales de carbonato de litio equivalente (LCE)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D24">
+      <c r="D25">
         <v>37</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Galan Lithium Ltd (Australia)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Galan Litio SA</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>30-71899846-4</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Litio</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Potasio y Litio</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Catamarca</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="M24">
+      <c r="M25">
         <v>292</v>
       </c>
-      <c r="N24">
+      <c r="N25">
         <v>217</v>
       </c>
-      <c r="O24">
+      <c r="O25">
         <v>217</v>
       </c>
-      <c r="P24">
+      <c r="P25">
         <v>31.112863</v>
       </c>
-      <c r="Q24">
+      <c r="Q25">
         <v>51.531371</v>
       </c>
-      <c r="R24">
+      <c r="R25">
         <v>82.644234</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="T24">
+      <c r="T25">
         <v>670</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U25" s="2">
         <v>47483</v>
       </c>
-      <c r="V24" s="2">
+      <c r="V25" s="2">
         <v>45594</v>
       </c>
-      <c r="W24" s="2">
+      <c r="W25" s="2">
         <v>45855</v>
       </c>
-      <c r="X24" s="2">
+      <c r="X25" s="2">
         <v>45896</v>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Res. 1271/2025</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/330470/20250828</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Res. 1271/2025; Globaris; MECON</t>
         </is>

--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -2401,7 +2401,7 @@
         <v>47330</v>
       </c>
       <c r="V18" s="2">
-        <v>45595</v>
+        <v>45978</v>
       </c>
       <c r="W18" s="2">
         <v>46185</v>

--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB25"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -1974,79 +1974,76 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ampliación Caucharí Olaroz</t>
+          <t>Bajo del Choique–La Invernada</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Que conforme surge de la presentación, se trata de la ampliación de un proyecto preexistente denominado Cauchari Olaroz con una capacidad productiva instalada de cuarenta mil toneladas (40.000 t) por año de carbonato de litio equivalente (en adelante LCE).</t>
+          <t>Exploración, producción, tratamiento y transporte de hidrocarburos en un área aproximada de 400 km² del centro-norte de Neuquén. El alcance comprende 620 pozos horizontales, cuatro plantas de tratamiento temprano (EPF), un oleoducto de 45 km y un gasoducto de 20 km, con capacidad total de 100.000 barriles diarios de petróleo y 12 millones de Sm³ diarios de gas. La primera etapa prevé 206 pozos y las EPF 1 y 2; la segunda, 414 pozos y las EPF 3 y 4.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ganfeng (China); Lithium Argentina (Suiza); JEMSE (Argentina)</t>
+          <t>Pluspetrol (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Minera Exar Sucursal Dedicada (“EXARSD”)</t>
+          <t>Gas y Petróleo del Neuquén S.A. - Pluspetrol Cuenca Neuquina S.R.L. – Unión Transitoria Exploración y Producción Bajo del Choique – La Invernada</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30-71924298-3</t>
+          <t>30-71920381-3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Minerales de primera categoría del Código de Minería de la Nación (potasio y litio)</t>
+          <t>Explotación y producción de nuevos desarrollos de hidrocarburos líquidos y gaseosos costa adentro, con instalaciones complementarias de tratamiento y transporte</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Centro-norte de Neuquén, aproximadamente 40 km al sur de Rincón de los Sauces; Hub Norte de la Cuenca Neuquina</t>
         </is>
       </c>
       <c r="M15">
-        <v>1241</v>
+        <v>12240</v>
       </c>
       <c r="N15">
-        <v>1167</v>
-      </c>
-      <c r="O15">
-        <v>1167</v>
+        <v>12240</v>
       </c>
       <c r="P15">
-        <v>37.96759</v>
+        <v>635</v>
       </c>
       <c r="Q15">
-        <v>58.787877</v>
+        <v>892</v>
       </c>
       <c r="R15">
-        <v>96.75546700000001</v>
+        <v>1527</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2054,109 +2051,117 @@
         </is>
       </c>
       <c r="T15">
-        <v>1787</v>
+        <v>2301</v>
       </c>
       <c r="U15" s="2">
-        <v>47665</v>
+        <v>47238</v>
       </c>
       <c r="V15" s="2">
-        <v>45795</v>
+        <v>46135</v>
       </c>
       <c r="W15" s="2">
-        <v>46151</v>
+        <v>46275</v>
       </c>
       <c r="X15" s="2">
-        <v>46177</v>
+        <v>46314</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Res. 825/2026</t>
+          <t>Res. 1808/2026</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/342818/20260605</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349233/20261019</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Res. 825/2026, Globaris; MECON</t>
+          <t>Res. 1808/2026; Gobierno de la Provincia del Neuquén; Casa Rosada</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/normativa/nacional/norma-431356; https://www.neuqueninforma.gob.ar/noticias/2026/10/19/265814-vaca-muerta-acelera-su-expansion-aprobaron-el-ingreso-al-rigi-de-un-proyecto-de-12-mil-millones-de-dolares; https://www.casarosada.gob.ar/informacion/conferencias/51404-conferencia-de-prensa-del-vocero-presidencial-adrian-ravier-desde-casa-rosada-19-10-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UT RIGI LOS TOLDOS</t>
+          <t>Ampliación Caucharí Olaroz</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Desarrollo de hidrocarburos en el área Los Toldos II Este, Vaca Muerta, el cual consiste en la perforación de 380 pozos junto con su infraestructura asociada para el tratamiento de la producción por una capacidad máxima de 70 mil barriles de petróleo diarios. El proyecto prevé un total de 360 millones de barriles de petróleo de exportación durante su operación.</t>
+          <t>Que conforme surge de la presentación, se trata de la ampliación de un proyecto preexistente denominado Cauchari Olaroz con una capacidad productiva instalada de cuarenta mil toneladas (40.000 t) por año de carbonato de litio equivalente (en adelante LCE).</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tecpetrol S.A. (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
+          <t>Ganfeng (China); Lithium Argentina (Suiza); JEMSE (Argentina)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tecpetrol S.A. Gas y Petróleo del Neuquén S.A. UT RIGI Los Toldos U.T.E.</t>
+          <t>Minera Exar Sucursal Dedicada (“EXARSD”)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>33-71889684-9</t>
+          <t>30-71924298-3</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Explotación y producción de nuevos desarrollos de hidrocarburos líquidos y gaseosos costa adentro</t>
+          <t>Minerales de primera categoría del Código de Minería de la Nación (potasio y litio)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Jujuy</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Departamento Pehuenches; área Los Toldos II Este; Engolfamiento/Bajo de Añelo</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="M16">
-        <v>6432</v>
+        <v>1241</v>
       </c>
       <c r="N16">
-        <v>6432</v>
+        <v>1167</v>
+      </c>
+      <c r="O16">
+        <v>1167</v>
       </c>
       <c r="P16">
-        <v>1182.281332</v>
+        <v>37.96759</v>
       </c>
       <c r="Q16">
-        <v>577.9334679999999</v>
+        <v>58.787877</v>
       </c>
       <c r="R16">
-        <v>1760.2148</v>
+        <v>96.75546700000001</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2164,50 +2169,45 @@
         </is>
       </c>
       <c r="T16">
-        <v>7900</v>
+        <v>1787</v>
       </c>
       <c r="U16" s="2">
-        <v>46630</v>
+        <v>47665</v>
       </c>
       <c r="V16" s="2">
-        <v>46101</v>
+        <v>45795</v>
       </c>
       <c r="W16" s="2">
-        <v>46274</v>
+        <v>46151</v>
       </c>
       <c r="X16" s="2">
-        <v>46304</v>
+        <v>46177</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Res. 1771/2026</t>
+          <t>Res. 825/2026</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/348768/20261009</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/342818/20260605</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Res. 1771/2026; Tecpetrol</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>https://www.argentina.gob.ar/normativa/nacional/norma-431089 ; https://www.tecpetrol.com/es/noticias/2026/rigi-los-toldos-ii-este</t>
+          <t>Res. 825/2026, Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Proyecto Rincón de Aranda (RDA)</t>
+          <t>UT RIGI LOS TOLDOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Consiste en: (i) la explotación de nuevos pozos hidrocarburíferos en el área RDA; (ii) el desarrollo, operación y/o prestación del servicio de tratamiento, procesamiento, almacenamiento y transporte del petróleo, gas natural y agua extraídos por PAMPA ENERGÍA SOCIEDAD ANÓNIMA - SUCURSAL DEDICADA PROYECTO RDA del área RDA y/o prestados a terceros, y la disposición final del agua incluyendo, la construcción y operación de plantas, oleoductos y gasoductos; y en (iii) la exportación y/o comercialización de los hidrocarburos y sus derivados obtenidos de la explotación de los nuevos pozos a desarrollarse en el área RDA.</t>
+          <t>Desarrollo de hidrocarburos en el área Los Toldos II Este, Vaca Muerta, el cual consiste en la perforación de 380 pozos junto con su infraestructura asociada para el tratamiento de la producción por una capacidad máxima de 70 mil barriles de petróleo diarios. El proyecto prevé un total de 360 millones de barriles de petróleo de exportación durante su operación.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pampa Energía (Argentina)</t>
+          <t>Tecpetrol S.A. (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sucursal Dedicada Midstream RDA</t>
+          <t>Tecpetrol S.A. Gas y Petróleo del Neuquén S.A. UT RIGI Los Toldos U.T.E.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30-71901911-7</t>
+          <t>33-71889684-9</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Explotación y Producción de Hidrocarburos Líquidos y Gaseosos Costa Adentro</t>
+          <t>Explotación y producción de nuevos desarrollos de hidrocarburos líquidos y gaseosos costa adentro</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2255,26 +2255,23 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Departamento Pehuenches; área Los Toldos II Este; Engolfamiento/Bajo de Añelo</t>
         </is>
       </c>
       <c r="M17">
-        <v>4522</v>
+        <v>6432</v>
       </c>
       <c r="N17">
-        <v>4521</v>
-      </c>
-      <c r="O17">
-        <v>4521</v>
+        <v>6432</v>
       </c>
       <c r="P17">
-        <v>521</v>
+        <v>1182.281332</v>
       </c>
       <c r="Q17">
-        <v>578</v>
+        <v>577.9334679999999</v>
       </c>
       <c r="R17">
-        <v>1099</v>
+        <v>1760.2148</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2282,112 +2279,117 @@
         </is>
       </c>
       <c r="T17">
-        <v>1733</v>
+        <v>7900</v>
       </c>
       <c r="U17" s="2">
-        <v>48030</v>
+        <v>46630</v>
       </c>
       <c r="V17" s="2">
-        <v>46090</v>
+        <v>46101</v>
       </c>
       <c r="W17" s="2">
-        <v>46198</v>
+        <v>46274</v>
       </c>
       <c r="X17" s="2">
-        <v>46224</v>
+        <v>46304</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Res. 1025/2026</t>
+          <t>Res. 1771/2026</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/344628/20260721</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/348768/20261009</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Res. 1025/2026; Globaris; MECON</t>
+          <t>Res. 1771/2026; Tecpetrol</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/normativa/nacional/norma-431089 ; https://www.tecpetrol.com/es/noticias/2026/rigi-los-toldos-ii-este</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sal de Oro II</t>
+          <t>Proyecto Rincón de Aranda (RDA)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Construcción de una planta destinada a la producción de carbonato de litio y su infraestructura complementaria. La planta tendrá una capacidad operativa aproximada de 23.000 toneladas anuales, que se obtendrá a través de un proceso convencional de evaporación solar y tratamiento químico de salmuera.</t>
+          <t>Consiste en: (i) la explotación de nuevos pozos hidrocarburíferos en el área RDA; (ii) el desarrollo, operación y/o prestación del servicio de tratamiento, procesamiento, almacenamiento y transporte del petróleo, gas natural y agua extraídos por PAMPA ENERGÍA SOCIEDAD ANÓNIMA - SUCURSAL DEDICADA PROYECTO RDA del área RDA y/o prestados a terceros, y la disposición final del agua incluyendo, la construcción y operación de plantas, oleoductos y gasoductos; y en (iii) la exportación y/o comercialización de los hidrocarburos y sus derivados obtenidos de la explotación de los nuevos pozos a desarrollarse en el área RDA.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Posco (Corea del Sur)</t>
+          <t>Pampa Energía (Argentina)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Posco Argentina SAU SDE</t>
+          <t>Sucursal Dedicada Midstream RDA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>30-71922048-3</t>
+          <t>30-71901911-7</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Potasio y Litio</t>
+          <t>Explotación y Producción de Hidrocarburos Líquidos y Gaseosos Costa Adentro</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Salta; Catamarca</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="M18">
-        <v>547</v>
+        <v>4522</v>
       </c>
       <c r="N18">
-        <v>547</v>
+        <v>4521</v>
       </c>
       <c r="O18">
-        <v>208</v>
+        <v>4521</v>
       </c>
       <c r="P18">
-        <v>90.916876</v>
+        <v>521</v>
       </c>
       <c r="Q18">
-        <v>7.083124</v>
+        <v>578</v>
       </c>
       <c r="R18">
-        <v>98</v>
+        <v>1099</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2395,63 +2397,68 @@
         </is>
       </c>
       <c r="T18">
-        <v>2335</v>
+        <v>1733</v>
       </c>
       <c r="U18" s="2">
-        <v>47330</v>
+        <v>48030</v>
       </c>
       <c r="V18" s="2">
-        <v>45978</v>
+        <v>46090</v>
       </c>
       <c r="W18" s="2">
-        <v>46185</v>
+        <v>46198</v>
       </c>
       <c r="X18" s="2">
-        <v>46234</v>
+        <v>46224</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Res. 1157/2026</t>
+          <t>Res. 1025/2026</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345279/20260731</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/344628/20260721</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Res. 1157/2026; Globaris; MECON</t>
+          <t>Res. 1025/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Proyecto de la Sucursal Dedicada de Liex S.A.</t>
+          <t>Sal de Oro II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Construcción y operación de una planta de proceso y de la infraestructura asociada, diseñadas para alcanzar una capacidad de producción de cuarenta mil (40.000) toneladas anuales de carbonato de litio mediante el método de extracción directa</t>
+          <t>Construcción de una planta destinada a la producción de carbonato de litio y su infraestructura complementaria. La planta tendrá una capacidad operativa aproximada de 23.000 toneladas anuales, que se obtendrá a través de un proceso convencional de evaporación solar y tratamiento químico de salmuera.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="D19">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zijin Mining (China)</t>
+          <t>Posco (Corea del Sur)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LIEX S.A.</t>
+          <t>Posco Argentina SAU SDE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>30-71929244-1</t>
+          <t>30-71922048-3</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2471,7 +2478,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Salta; Catamarca</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2480,22 +2487,22 @@
         </is>
       </c>
       <c r="M19">
-        <v>710</v>
+        <v>547</v>
       </c>
       <c r="N19">
-        <v>710</v>
+        <v>547</v>
       </c>
       <c r="O19">
-        <v>594</v>
+        <v>208</v>
       </c>
       <c r="P19">
-        <v>107.537</v>
+        <v>90.916876</v>
       </c>
       <c r="Q19">
-        <v>308.048</v>
+        <v>7.083124</v>
       </c>
       <c r="R19">
-        <v>415.585</v>
+        <v>98</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2503,68 +2510,63 @@
         </is>
       </c>
       <c r="T19">
-        <v>4406</v>
+        <v>2335</v>
       </c>
       <c r="U19" s="2">
-        <v>46721</v>
+        <v>47330</v>
       </c>
       <c r="V19" s="2">
-        <v>46063</v>
+        <v>45978</v>
       </c>
       <c r="W19" s="2">
-        <v>46206</v>
+        <v>46185</v>
       </c>
       <c r="X19" s="2">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Res. 1153/2026</t>
+          <t>Res. 1157/2026</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345075/20260729</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345279/20260731</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Res. 1153/2026; Globaris; MECON</t>
+          <t>Res. 1157/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Proyecto de la Sucursal Dedicada de Liex S.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Extracción, producción y exportación de cobre, oro y plata de los yacimientos Josemaría y Filo del Sol ubicados en la provincia de San Juan, República Argentina, así como la exploración de las concesiones mineras que forman parte del proyecto y el desarrollo de la infraestructura necesaria para su ejecución. Incluye infraestructura clave para operaciones de minería a cielo abierto: una planta concentradora para el procesamiento de minerales, instalaciones de lixiviación, infraestructura eléctrica, sistemas de suministro de agua, caminos de acceso y alojamientos.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Construcción y operación de una planta de proceso y de la infraestructura asociada, diseñadas para alcanzar una capacidad de producción de cuarenta mil (40.000) toneladas anuales de carbonato de litio mediante el método de extracción directa</t>
         </is>
       </c>
       <c r="D20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BHP (Australia); Lundin Mining (Canadá)</t>
+          <t>Zijin Mining (China)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vicuña Argentina S.A.</t>
+          <t>LIEX S.A.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>33-61913055-9</t>
+          <t>30-71929244-1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2574,41 +2576,41 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Cobre, Oro y Plata</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Minerales de primera y segunda categoría del Código de Minería de la Nación (excluidos potasio y litio)</t>
+          <t>Potasio y Litio</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cuyo</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="M20">
-        <v>9737</v>
+        <v>710</v>
       </c>
       <c r="N20">
-        <v>9737</v>
+        <v>710</v>
       </c>
       <c r="O20">
-        <v>9025</v>
+        <v>594</v>
       </c>
       <c r="P20">
-        <v>1004.6565</v>
+        <v>107.537</v>
       </c>
       <c r="Q20">
-        <v>1004.6565</v>
+        <v>308.048</v>
       </c>
       <c r="R20">
-        <v>2009.313</v>
+        <v>415.585</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2616,68 +2618,68 @@
         </is>
       </c>
       <c r="T20">
-        <v>31700</v>
+        <v>4406</v>
       </c>
       <c r="U20" s="2">
-        <v>47118</v>
+        <v>46721</v>
       </c>
       <c r="V20" s="2">
-        <v>46002</v>
+        <v>46063</v>
       </c>
       <c r="W20" s="2">
-        <v>46176</v>
+        <v>46206</v>
       </c>
       <c r="X20" s="2">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Res. 1154/2026</t>
+          <t>Res. 1153/2026</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345167/20260730</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345075/20260729</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Res. 1154/2026; Globaris; MECON</t>
+          <t>Res. 1153/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Proyecto Los Azules</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Desarrollo (factibilidad, permisos) y la construcción de mina, planta e infraestructura asociada para extraer y procesar cátodos de cobre</t>
+          <t>Extracción, producción y exportación de cobre, oro y plata de los yacimientos Josemaría y Filo del Sol ubicados en la provincia de San Juan, República Argentina, así como la exploración de las concesiones mineras que forman parte del proyecto y el desarrollo de la infraestructura necesaria para su ejecución. Incluye infraestructura clave para operaciones de minería a cielo abierto: una planta concentradora para el procesamiento de minerales, instalaciones de lixiviación, infraestructura eléctrica, sistemas de suministro de agua, caminos de acceso y alojamientos.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D21">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>McEwen Copper Inc. (Canadá)</t>
+          <t>BHP (Australia); Lundin Mining (Canadá)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Andes Corporación Minera SA (ACM)</t>
+          <t>Vicuña Argentina S.A.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>30-70952278-3</t>
+          <t>33-61913055-9</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2687,7 +2689,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Cobre, Oro y Plata</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2706,22 +2708,22 @@
         </is>
       </c>
       <c r="M21">
-        <v>2672</v>
+        <v>9737</v>
       </c>
       <c r="N21">
-        <v>2672</v>
+        <v>9737</v>
       </c>
       <c r="O21">
-        <v>2354</v>
+        <v>9025</v>
       </c>
       <c r="P21">
-        <v>33.51255105</v>
+        <v>1004.6565</v>
       </c>
       <c r="Q21">
-        <v>382.26276161</v>
+        <v>1004.6565</v>
       </c>
       <c r="R21">
-        <v>415.77531266</v>
+        <v>2009.313</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2729,45 +2731,45 @@
         </is>
       </c>
       <c r="T21">
-        <v>7391</v>
+        <v>31700</v>
       </c>
       <c r="U21" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="V21" s="2">
-        <v>45849</v>
+        <v>46002</v>
       </c>
       <c r="W21" s="2">
-        <v>45925</v>
+        <v>46176</v>
       </c>
       <c r="X21" s="2">
-        <v>45943</v>
+        <v>46233</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Res. 1553/2025</t>
+          <t>Res. 1154/2026</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/332807/20251014</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345167/20260730</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Res. 1553/2025; Globaris; MECON</t>
+          <t>Res. 1154/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ampliación Mega</t>
+          <t>Proyecto Los Azules</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ampliación de un complejo industrial para incrementar la capacidad de producción de Líquidos del Gas Natural (LGN) en 1500 toneladas diarias.  El proyecto contempla nuevas instalaciones en la Planta de Separación de Loma La Lata, la ampliación de la capacidad de transporte del poliducto que atraviesa Neuquén, Río Negro, La Pampa y Buenos Aires, y la expansión de la Planta de Fraccionamiento ubicada en Bahía Blanca.</t>
+          <t>Desarrollo (factibilidad, permisos) y la construcción de mina, planta e infraestructura asociada para extraer y procesar cátodos de cobre</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2776,65 +2778,65 @@
         </is>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina); Petrobras (Brasil); Dow (Argentina)</t>
+          <t>McEwen Copper Inc. (Canadá)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Compañía Mega SA Sucursal Dedicada</t>
+          <t>Andes Corporación Minera SA (ACM)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>30-71932893-4</t>
+          <t>30-70952278-3</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Construcción de plantas de tratamiento, plantas de separación de líquidos de gas natural, oleoductos, gasoductos y poliductos e instalaciones de almacenamiento</t>
+          <t>Minerales de primera y segunda categoría del Código de Minería de la Nación (excluidos potasio y litio)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Neuquén; La Pampa; Río Negro; Buenos Aires</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Múltiples</t>
+          <t>Cuyo</t>
         </is>
       </c>
       <c r="M22">
-        <v>365.398669</v>
+        <v>2672</v>
       </c>
       <c r="N22">
-        <v>365.398669</v>
+        <v>2672</v>
       </c>
       <c r="O22">
-        <v>359.164361</v>
+        <v>2354</v>
       </c>
       <c r="P22">
-        <v>121.613889</v>
+        <v>33.51255105</v>
       </c>
       <c r="Q22">
-        <v>152.709106</v>
+        <v>382.26276161</v>
       </c>
       <c r="R22">
-        <v>274.322995</v>
+        <v>415.77531266</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2842,68 +2844,68 @@
         </is>
       </c>
       <c r="T22">
-        <v>792</v>
+        <v>7391</v>
       </c>
       <c r="U22" s="2">
-        <v>46661</v>
+        <v>46752</v>
       </c>
       <c r="V22" s="2">
-        <v>46099</v>
+        <v>45849</v>
       </c>
       <c r="W22" s="2">
-        <v>46231</v>
+        <v>45925</v>
       </c>
       <c r="X22" s="2">
-        <v>46260</v>
+        <v>45943</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Res. 1381/2026</t>
+          <t>Res. 1553/2025</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346397/20260826</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/332807/20251014</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Res. 1381/2026; Globaris; MECON</t>
+          <t>Res. 1553/2025; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fertilizantes</t>
+          <t>Ampliación Mega</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Construcción, operación y gerenciamiento de dos (2) plantas de producción de urea, cada una con capacidad de tres mil toneladas (3.000 t) por día, con sus correspondientes unidades de granulación, y una planta de amoníaco con capacidad de tres mil cuatrocientas cincuenta toneladas (3.450 t) por día, utilizando como insumo principal el gas natural de Vaca Muerta, a desarrollarse en el Puerto de Ingeniero White, partido de Bahía Blanca, provincia de Buenos Aires.</t>
+          <t>Ampliación de un complejo industrial para incrementar la capacidad de producción de Líquidos del Gas Natural (LGN) en 1500 toneladas diarias.  El proyecto contempla nuevas instalaciones en la Planta de Separación de Loma La Lata, la ampliación de la capacidad de transporte del poliducto que atraviesa Neuquén, Río Negro, La Pampa y Buenos Aires, y la expansión de la Planta de Fraccionamiento ubicada en Bahía Blanca.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D23">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pampa Energía (Argentina)</t>
+          <t>YPF S.A. (Argentina); Petrobras (Brasil); Dow (Argentina)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fértil Pampa S.A.U.</t>
+          <t>Compañía Mega SA Sucursal Dedicada</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>30-71875855-2</t>
+          <t>30-71932893-4</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2913,41 +2915,41 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Petroquímica y Fertilizantes</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Petroquímica y Fertilizantes</t>
+          <t>Construcción de plantas de tratamiento, plantas de separación de líquidos de gas natural, oleoductos, gasoductos y poliductos e instalaciones de almacenamiento</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Neuquén; La Pampa; Río Negro; Buenos Aires</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Puerto de Ingeniero White, Bahía Blanca</t>
+          <t>Múltiples</t>
         </is>
       </c>
       <c r="M23">
-        <v>2693</v>
+        <v>365.398669</v>
       </c>
       <c r="N23">
-        <v>2693</v>
+        <v>365.398669</v>
       </c>
       <c r="O23">
-        <v>2693</v>
+        <v>359.164361</v>
       </c>
       <c r="P23">
-        <v>785</v>
+        <v>121.613889</v>
       </c>
       <c r="Q23">
-        <v>881</v>
+        <v>152.709106</v>
       </c>
       <c r="R23">
-        <v>1666</v>
+        <v>274.322995</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2955,68 +2957,68 @@
         </is>
       </c>
       <c r="T23">
-        <v>12500</v>
+        <v>792</v>
       </c>
       <c r="U23" s="2">
-        <v>47453</v>
+        <v>46661</v>
       </c>
       <c r="V23" s="2">
-        <v>46133</v>
+        <v>46099</v>
       </c>
       <c r="W23" s="2">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="X23" s="2">
-        <v>46272</v>
+        <v>46260</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Res. 1468/2026</t>
+          <t>Res. 1381/2026</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346966/20260907</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346397/20260826</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Res.1468/2026; MECON</t>
+          <t>Res. 1381/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
+          <t>Fertilizantes</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
+          <t>Construcción, operación y gerenciamiento de dos (2) plantas de producción de urea, cada una con capacidad de tres mil toneladas (3.000 t) por día, con sus correspondientes unidades de granulación, y una planta de amoníaco con capacidad de tres mil cuatrocientas cincuenta toneladas (3.450 t) por día, utilizando como insumo principal el gas natural de Vaca Muerta, a desarrollarse en el Puerto de Ingeniero White, partido de Bahía Blanca, provincia de Buenos Aires.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D24">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE) (Argentina)</t>
+          <t>Pampa Energía (Argentina)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>San Matías Pipeline S.A.</t>
+          <t>Fértil Pampa S.A.U.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t> 30-71703621-9</t>
+          <t>30-71875855-2</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3026,41 +3028,41 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Petroquímica y Fertilizantes</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Transporte y Almacenamiento</t>
+          <t>Petroquímica y Fertilizantes</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Río Negro; Neuquén</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Puerto de Ingeniero White, Bahía Blanca</t>
         </is>
       </c>
       <c r="M24">
-        <v>1300</v>
+        <v>2693</v>
       </c>
       <c r="N24">
-        <v>1300</v>
+        <v>2693</v>
       </c>
       <c r="O24">
-        <v>955</v>
+        <v>2693</v>
       </c>
       <c r="P24">
-        <v>454</v>
+        <v>785</v>
       </c>
       <c r="Q24">
-        <v>501</v>
+        <v>881</v>
       </c>
       <c r="R24">
-        <v>955</v>
+        <v>1666</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -3068,144 +3070,257 @@
         </is>
       </c>
       <c r="T24">
-        <v>2489</v>
+        <v>12500</v>
       </c>
       <c r="U24" s="2">
-        <v>46538</v>
+        <v>47453</v>
       </c>
       <c r="V24" s="2">
-        <v>45950</v>
+        <v>46133</v>
       </c>
       <c r="W24" s="2">
-        <v>46174</v>
+        <v>46237</v>
       </c>
       <c r="X24" s="2">
-        <v>46198</v>
+        <v>46272</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Res. 873/2026</t>
+          <t>Res. 1468/2026</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346966/20260907</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Res. 873/2026; Globaris; MECON</t>
+          <t>Res.1468/2026; MECON</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>36</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pan American Energy (PAE) (Argentina)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>San Matías Pipeline S.A.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t> 30-71703621-9</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Midstream</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Transporte y Almacenamiento</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Río Negro; Neuquén</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="M25">
+        <v>1300</v>
+      </c>
+      <c r="N25">
+        <v>1300</v>
+      </c>
+      <c r="O25">
+        <v>955</v>
+      </c>
+      <c r="P25">
+        <v>454</v>
+      </c>
+      <c r="Q25">
+        <v>501</v>
+      </c>
+      <c r="R25">
+        <v>955</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="T25">
+        <v>2489</v>
+      </c>
+      <c r="U25" s="2">
+        <v>46538</v>
+      </c>
+      <c r="V25" s="2">
+        <v>45950</v>
+      </c>
+      <c r="W25" s="2">
+        <v>46174</v>
+      </c>
+      <c r="X25" s="2">
+        <v>46198</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Res. 873/2026</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Res. 873/2026; Globaris; MECON</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Hombre Muerto Oeste (HMW)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Producción de doce mil (12.000) toneladas anuales de carbonato de litio equivalente (LCE)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D25">
+      <c r="D26">
         <v>37</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Galan Lithium Ltd (Australia)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Galan Litio SA</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>30-71899846-4</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Litio</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Potasio y Litio</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Catamarca</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="M25">
+      <c r="M26">
         <v>292</v>
       </c>
-      <c r="N25">
+      <c r="N26">
         <v>217</v>
       </c>
-      <c r="O25">
+      <c r="O26">
         <v>217</v>
       </c>
-      <c r="P25">
+      <c r="P26">
         <v>31.112863</v>
       </c>
-      <c r="Q25">
+      <c r="Q26">
         <v>51.531371</v>
       </c>
-      <c r="R25">
+      <c r="R26">
         <v>82.644234</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="T25">
+      <c r="T26">
         <v>670</v>
       </c>
-      <c r="U25" s="2">
+      <c r="U26" s="2">
         <v>47483</v>
       </c>
-      <c r="V25" s="2">
+      <c r="V26" s="2">
         <v>45594</v>
       </c>
-      <c r="W25" s="2">
+      <c r="W26" s="2">
         <v>45855</v>
       </c>
-      <c r="X25" s="2">
+      <c r="X26" s="2">
         <v>45896</v>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Res. 1271/2025</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/330470/20250828</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>Res. 1271/2025; Globaris; MECON</t>
         </is>

--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Consiste en la construcción y desarrollo de un oleoducto, Iincrementar la capacidad de transporte y almacenamiento de petróleo crudo viabilizando la exportación de hidrocarburos provenientes de la formación “Vaca Muerta”</t>
+          <t>Consiste en la construcción y desarrollo de un oleoducto, incrementar la capacidad de transporte y almacenamiento de petróleo crudo viabilizando la exportación de hidrocarburos provenientes de la formación “Vaca Muerta”</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3323,6 +3323,124 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>Res. 1271/2025; Globaris; MECON</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ampliación de la planta industrial de Toyota en Zárate mediante la construcción, instalación, puesta en funcionamiento y operación de una tercera planta para fabricar un vehículo híbrido eléctrico no enchufable (full HEV), inicialmente tipo pick-up y con posibilidad de versión SUV.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>42</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Toyota Argentina S.A. (Argentina)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Toyota Argentina S.A. Sucursal Dedicada</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>30-71944240-0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Automotriz</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Fabricación, ensamblado y montaje de vehículos de nueva tecnología de motorización</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Zárate</t>
+        </is>
+      </c>
+      <c r="M27">
+        <v>1341</v>
+      </c>
+      <c r="N27">
+        <v>1252.926108</v>
+      </c>
+      <c r="O27">
+        <v>1252.926108</v>
+      </c>
+      <c r="P27">
+        <v>19.5</v>
+      </c>
+      <c r="Q27">
+        <v>147.753031</v>
+      </c>
+      <c r="R27">
+        <v>167.253031</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="T27">
+        <v>6225</v>
+      </c>
+      <c r="U27" s="2">
+        <v>47026</v>
+      </c>
+      <c r="V27" s="2">
+        <v>46181</v>
+      </c>
+      <c r="W27" s="2">
+        <v>46294</v>
+      </c>
+      <c r="X27" s="2">
+        <v>46317</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Res. 1848/2026</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349428/20261022</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Res. 1848/2026 (B.O. 22/10/2026); Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026)</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349428/20261022; https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/</t>
         </is>
       </c>
     </row>

--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB27"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rincón Mining Pty Ltd.</t>
+          <t>RIGI - RINCON MINING PTY LIMITED</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30-70708643-9</t>
+          <t>30-71899954-1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2990,79 +2990,79 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fertilizantes</t>
+          <t>Minera Agua Rica</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Construcción, operación y gerenciamiento de dos (2) plantas de producción de urea, cada una con capacidad de tres mil toneladas (3.000 t) por día, con sus correspondientes unidades de granulación, y una planta de amoníaco con capacidad de tres mil cuatrocientas cincuenta toneladas (3.450 t) por día, utilizando como insumo principal el gas natural de Vaca Muerta, a desarrollarse en el Puerto de Ingeniero White, partido de Bahía Blanca, provincia de Buenos Aires.</t>
+          <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D24">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pampa Energía (Argentina)</t>
+          <t>Glencore (Suiza)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fértil Pampa S.A.U.</t>
+          <t>Minera Agua Rica LLC Sucursal Argentina</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>30-71875855-2</t>
+          <t>30-70769036-0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Petroquímica y Fertilizantes</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Petroquímica y Fertilizantes</t>
+          <t>Minerales de primera y segunda categoría del Código de Minería de la Nación (excluidos potasio y litio)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Puerto de Ingeniero White, Bahía Blanca</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="M24">
-        <v>2693</v>
+        <v>6394</v>
       </c>
       <c r="N24">
-        <v>2693</v>
+        <v>6393.631995</v>
       </c>
       <c r="O24">
-        <v>2693</v>
+        <v>3310.574165</v>
       </c>
       <c r="P24">
-        <v>785</v>
+        <v>111.63955213</v>
       </c>
       <c r="Q24">
-        <v>881</v>
+        <v>659.8944598</v>
       </c>
       <c r="R24">
-        <v>1666</v>
+        <v>771.53401193</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -3070,68 +3070,73 @@
         </is>
       </c>
       <c r="T24">
-        <v>12500</v>
+        <v>8200</v>
       </c>
       <c r="U24" s="2">
-        <v>47453</v>
+        <v>47118</v>
       </c>
       <c r="V24" s="2">
-        <v>46133</v>
+        <v>45887</v>
       </c>
       <c r="W24" s="2">
-        <v>46237</v>
+        <v>46295</v>
       </c>
       <c r="X24" s="2">
-        <v>46272</v>
+        <v>46322</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Res. 1468/2026</t>
+          <t>Res. 1854/2026</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346966/20260907</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349616/20261027</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Res.1468/2026; MECON</t>
+          <t>Globaris; Glencore; Luis Caputo; Reuters; Res. 1854/2026; Boletín Oficial; TN</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.boletinoficial.gob.ar/detalleAviso/primera/349616/20261027; https://www.cda.org.ar/detalle_normativa.php?id=9497; https://tn.com.ar/economia/2026/10/27/el-gobierno-aprobo-el-ingreso-al-rigi-de-un-proyecto-minero-de-us6393-millones-en-catamarca/?outputType=amp</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
+          <t>Fertilizantes</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
+          <t>Construcción, operación y gerenciamiento de dos (2) plantas de producción de urea, cada una con capacidad de tres mil toneladas (3.000 t) por día, con sus correspondientes unidades de granulación, y una planta de amoníaco con capacidad de tres mil cuatrocientas cincuenta toneladas (3.450 t) por día, utilizando como insumo principal el gas natural de Vaca Muerta, a desarrollarse en el Puerto de Ingeniero White, partido de Bahía Blanca, provincia de Buenos Aires.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D25">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE) (Argentina)</t>
+          <t>Pampa Energía (Argentina)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>San Matías Pipeline S.A.</t>
+          <t>Fértil Pampa S.A.U.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t> 30-71703621-9</t>
+          <t>30-71875855-2</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3141,41 +3146,41 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Petroquímica y Fertilizantes</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Transporte y Almacenamiento</t>
+          <t>Petroquímica y Fertilizantes</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Río Negro; Neuquén</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Puerto de Ingeniero White, Bahía Blanca</t>
         </is>
       </c>
       <c r="M25">
-        <v>1300</v>
+        <v>2693</v>
       </c>
       <c r="N25">
-        <v>1300</v>
+        <v>2693</v>
       </c>
       <c r="O25">
-        <v>955</v>
+        <v>2693</v>
       </c>
       <c r="P25">
-        <v>454</v>
+        <v>785</v>
       </c>
       <c r="Q25">
-        <v>501</v>
+        <v>881</v>
       </c>
       <c r="R25">
-        <v>955</v>
+        <v>1666</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -3183,45 +3188,45 @@
         </is>
       </c>
       <c r="T25">
-        <v>2489</v>
+        <v>12500</v>
       </c>
       <c r="U25" s="2">
-        <v>46538</v>
+        <v>47453</v>
       </c>
       <c r="V25" s="2">
-        <v>45950</v>
+        <v>46133</v>
       </c>
       <c r="W25" s="2">
-        <v>46174</v>
+        <v>46237</v>
       </c>
       <c r="X25" s="2">
-        <v>46198</v>
+        <v>46272</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Res. 873/2026</t>
+          <t>Res. 1468/2026</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346966/20260907</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Res. 873/2026; Globaris; MECON</t>
+          <t>Res.1468/2026; MECON</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hombre Muerto Oeste (HMW)</t>
+          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Producción de doce mil (12.000) toneladas anuales de carbonato de litio equivalente (LCE)</t>
+          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3230,65 +3235,65 @@
         </is>
       </c>
       <c r="D26">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Galan Lithium Ltd (Australia)</t>
+          <t>Pan American Energy (PAE) (Argentina)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Galan Litio SA</t>
+          <t>San Matías Pipeline S.A.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>30-71899846-4</t>
+          <t> 30-71703621-9</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Potasio y Litio</t>
+          <t>Transporte y Almacenamiento</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Río Negro; Neuquén</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="M26">
-        <v>292</v>
+        <v>1300</v>
       </c>
       <c r="N26">
-        <v>217</v>
+        <v>1300</v>
       </c>
       <c r="O26">
-        <v>217</v>
+        <v>955</v>
       </c>
       <c r="P26">
-        <v>31.112863</v>
+        <v>454</v>
       </c>
       <c r="Q26">
-        <v>51.531371</v>
+        <v>501</v>
       </c>
       <c r="R26">
-        <v>82.644234</v>
+        <v>955</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -3296,149 +3301,262 @@
         </is>
       </c>
       <c r="T26">
-        <v>670</v>
+        <v>2489</v>
       </c>
       <c r="U26" s="2">
-        <v>47483</v>
+        <v>46538</v>
       </c>
       <c r="V26" s="2">
-        <v>45594</v>
+        <v>45950</v>
       </c>
       <c r="W26" s="2">
-        <v>45855</v>
+        <v>46174</v>
       </c>
       <c r="X26" s="2">
-        <v>45896</v>
+        <v>46198</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Res. 1271/2025</t>
+          <t>Res. 873/2026</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/330470/20250828</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Res. 1271/2025; Globaris; MECON</t>
+          <t>Res. 873/2026; Globaris; MECON</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Hombre Muerto Oeste (HMW)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Producción de doce mil (12.000) toneladas anuales de carbonato de litio equivalente (LCE)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>37</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Galan Lithium Ltd (Australia)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Galan Litio SA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>30-71899846-4</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Minería</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Litio</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Potasio y Litio</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Catamarca</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NOA</t>
+        </is>
+      </c>
+      <c r="M27">
+        <v>292</v>
+      </c>
+      <c r="N27">
+        <v>217</v>
+      </c>
+      <c r="O27">
+        <v>217</v>
+      </c>
+      <c r="P27">
+        <v>31.112863</v>
+      </c>
+      <c r="Q27">
+        <v>51.531371</v>
+      </c>
+      <c r="R27">
+        <v>82.644234</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="T27">
+        <v>670</v>
+      </c>
+      <c r="U27" s="2">
+        <v>47483</v>
+      </c>
+      <c r="V27" s="2">
+        <v>45594</v>
+      </c>
+      <c r="W27" s="2">
+        <v>45855</v>
+      </c>
+      <c r="X27" s="2">
+        <v>45896</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Res. 1271/2025</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/330470/20250828</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Res. 1271/2025; Globaris; MECON</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Toyota</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Ampliación de la planta industrial de Toyota en Zárate mediante la construcción, instalación, puesta en funcionamiento y operación de una tercera planta para fabricar un vehículo híbrido eléctrico no enchufable (full HEV), inicialmente tipo pick-up y con posibilidad de versión SUV.</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D27">
+      <c r="D28">
         <v>42</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Toyota Argentina S.A. (Argentina)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Toyota Argentina S.A. Sucursal Dedicada</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>30-71944240-0</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Automotriz</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Fabricación, ensamblado y montaje de vehículos de nueva tecnología de motorización</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Buenos Aires</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Zárate</t>
         </is>
       </c>
-      <c r="M27">
+      <c r="M28">
         <v>1341</v>
       </c>
-      <c r="N27">
+      <c r="N28">
         <v>1252.926108</v>
       </c>
-      <c r="O27">
+      <c r="O28">
         <v>1252.926108</v>
       </c>
-      <c r="P27">
+      <c r="P28">
         <v>19.5</v>
       </c>
-      <c r="Q27">
+      <c r="Q28">
         <v>147.753031</v>
       </c>
-      <c r="R27">
+      <c r="R28">
         <v>167.253031</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="T27">
+      <c r="T28">
         <v>6225</v>
       </c>
-      <c r="U27" s="2">
+      <c r="U28" s="2">
         <v>47026</v>
       </c>
-      <c r="V27" s="2">
+      <c r="V28" s="2">
         <v>46181</v>
       </c>
-      <c r="W27" s="2">
+      <c r="W28" s="2">
         <v>46294</v>
       </c>
-      <c r="X27" s="2">
+      <c r="X28" s="2">
         <v>46317</v>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Res. 1848/2026</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349428/20261022</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>Res. 1848/2026 (B.O. 22/10/2026); Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026)</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349428/20261022; https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/</t>
         </is>
